--- a/samples/ss_pmlng_ingest.xlsx
+++ b/samples/ss_pmlng_ingest.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T12"/>
+  <dimension ref="A1:U12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -536,65 +536,70 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Bus 150 kV</t>
+          <t>Bus HV</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Bus LV</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Jumlah Trafo</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Kapasitor</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Catatan Simbol</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Sirkit Bay</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Status Operasi</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Status Kerawanan</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>No Kerawanan</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Wilayah</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Sudut Pandang</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Latitude</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Longitude</t>
         </is>
@@ -633,24 +638,25 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -686,41 +692,46 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>PMLNG7</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>NBTNG</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>2</v>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
         <is>
           <t>2 IBT (unit 1,2)</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -753,30 +764,31 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
         <is>
           <t>2x60 MVA</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr">
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -809,30 +821,31 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
         <is>
           <t>2x60 MVA</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -865,30 +878,31 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
         <is>
           <t>2x60 MVA</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -921,34 +935,35 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
         <is>
           <t>30/60/60 MVA + 25 MVAR</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -981,34 +996,35 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
         <is>
           <t>3x60 MVA + 25 MVAR</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1041,30 +1057,31 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
         <is>
           <t>60 MVA</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr">
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1097,34 +1114,35 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
         <is>
           <t>3x60 MVA + 25 MVAR (kapasitor 1 PMS busbar)</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr">
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1157,30 +1175,31 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
         <is>
           <t>60 MVA</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr">
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr">
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1213,38 +1232,39 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
         <is>
           <t>batas ke Subsistem Mandirancan (UP2B Jabar)</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>SOURCE_BOUNDARY</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/samples/ss_pmlng_ingest.xlsx
+++ b/samples/ss_pmlng_ingest.xlsx
@@ -10,8 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gardu_Induk_dan_Aset" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jalur_Transmisi" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bay" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Kerawanan_Detail" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Kerawanan_Detail" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U12"/>
+  <dimension ref="A1:U13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -664,7 +663,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IBT 1,2 Pemalang 500/150 kV</t>
+          <t>IBT 1 Pemalang 500/150 kV</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -701,14 +700,10 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2 IBT (unit 1,2)</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
@@ -739,37 +734,47 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>New Batang (bus 150 kV)</t>
+          <t>IBT 2 Pemalang 500/150 kV</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>IBT 2 PMLNG7</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>IBT 3-Winding</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>PMLNG7</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>NBTNG</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Busbar GI</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>2x60 MVA</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
@@ -796,12 +801,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bumi Putih</t>
+          <t>New Batang (bus 150 kV)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BNPTH</t>
+          <t>NBTNG</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -810,7 +815,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -853,12 +858,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Weleri</t>
+          <t>Bumi Putih</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>WLERI</t>
+          <t>BNPTH</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -867,7 +872,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -910,12 +915,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Batang</t>
+          <t>Weleri</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BTANG</t>
+          <t>WLERI</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -924,7 +929,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -938,7 +943,7 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>30/60/60 MVA + 25 MVAR</t>
+          <t>2x60 MVA</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -950,14 +955,10 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -971,12 +972,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pekalongan</t>
+          <t>Batang</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PKLON</t>
+          <t>BTANG</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -985,7 +986,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -999,7 +1000,7 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>3x60 MVA + 25 MVAR</t>
+          <t>30/60/60 MVA + 25 MVAR</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -1032,12 +1033,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Comal</t>
+          <t>Pekalongan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>COMAL</t>
+          <t>PKLON</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1046,7 +1047,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1060,7 +1061,7 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>60 MVA</t>
+          <t>3x60 MVA + 25 MVAR</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -1072,10 +1073,14 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1089,12 +1094,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pemalang</t>
+          <t>Comal</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PMLNG</t>
+          <t>COMAL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1103,7 +1108,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1117,7 +1122,7 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>3x60 MVA + 25 MVAR (kapasitor 1 PMS busbar)</t>
+          <t>60 MVA</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -1129,14 +1134,10 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1150,12 +1151,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tarub</t>
+          <t>Pemalang</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TARUB</t>
+          <t>PMLNG</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1164,7 +1165,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1178,7 +1179,7 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>60 MVA</t>
+          <t>3x60 MVA + 25 MVAR (kapasitor 1 PMS busbar)</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -1190,10 +1191,14 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="R11" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1207,12 +1212,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kebasen</t>
+          <t>Tarub</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>KBSEN</t>
+          <t>TARUB</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1221,7 +1226,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1235,7 +1240,7 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>batas ke Subsistem Mandirancan (UP2B Jabar)</t>
+          <t>60 MVA</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -1244,27 +1249,84 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kebasen</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>KBSEN</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Busbar GI</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>batas ke Subsistem Mandirancan (UP2B Jabar)</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
         <is>
           <t>SOURCE_BOUNDARY</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1277,7 +1339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1394,7 +1456,7 @@
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -1433,12 +1495,12 @@
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SUTT Bumi Putih - Weleri</t>
+          <t>SUTT New Batang - Weleri Bus 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>BNPTH</t>
+          <t>NBTNG</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1453,7 +1515,7 @@
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -1473,7 +1535,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
         <v>3</v>
@@ -1492,17 +1554,17 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SUTT New Batang - Batang</t>
+          <t>SUTT Bumi Putih - Weleri</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NBTNG</t>
+          <t>BNPTH</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>BTANG</t>
+          <t>WLERI</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1512,7 +1574,7 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -1532,10 +1594,10 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -1548,24 +1610,20 @@
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SUTT Batang - Pekalongan</t>
+          <t>SUTT New Batang - Batang</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>NBTNG</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>BTANG</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>PKLON</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1584,7 +1642,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Sangat Rawan</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1595,10 +1653,10 @@
         </is>
       </c>
       <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
         <v>2</v>
-      </c>
-      <c r="O5" t="n">
-        <v>3</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -1611,20 +1669,24 @@
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SUTT Pekalongan - Comal</t>
+          <t>SUTT Batang - Pekalongan</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>BTANG</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>PKLON</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>COMAL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1643,7 +1705,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Sangat Rawan</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1654,10 +1716,10 @@
         </is>
       </c>
       <c r="N6" t="n">
+        <v>2</v>
+      </c>
+      <c r="O6" t="n">
         <v>3</v>
-      </c>
-      <c r="O6" t="n">
-        <v>4</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -1673,17 +1735,17 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SUTT Comal - Pemalang</t>
+          <t>SUTT Pekalongan - Comal</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>PKLON</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>COMAL</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>PMLNG</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1713,10 +1775,10 @@
         </is>
       </c>
       <c r="N7" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" t="n">
         <v>4</v>
-      </c>
-      <c r="O7" t="n">
-        <v>5</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1732,17 +1794,17 @@
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SUTT Pemalang - Tarub</t>
+          <t>SUTT Comal - Pemalang</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>COMAL</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>PMLNG</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>TARUB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1772,10 +1834,10 @@
         </is>
       </c>
       <c r="N8" t="n">
+        <v>4</v>
+      </c>
+      <c r="O8" t="n">
         <v>5</v>
-      </c>
-      <c r="O8" t="n">
-        <v>6</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -1788,24 +1850,20 @@
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SUTT Tarub - Kebasen</t>
+          <t>SUTT Pemalang - Tarub</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>PMLNG</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>TARUB</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>KBSEN</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1824,7 +1882,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Sangat Rawan</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1835,17 +1893,80 @@
         </is>
       </c>
       <c r="N9" t="n">
+        <v>5</v>
+      </c>
+      <c r="O9" t="n">
         <v>6</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SUTT Tarub - Kebasen</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TARUB</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>KBSEN</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Sangat Rawan</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>6</v>
+      </c>
+      <c r="O10" t="n">
         <v>7</v>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1858,137 +1979,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Kode GI</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Nama GI</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Feeder (GI Induk)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Tegangan</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Jumlah Sirkit</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Status Operasi</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>No Kerawanan</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Sudut Pandang</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>TJATI7</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>GITET Tanjungjati (500 kV)</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>PMLNG7</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>MDCAN7</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>GITET Mandirancan (500 kV)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>PMLNG7</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>4</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/samples/ss_pmlng_ingest.xlsx
+++ b/samples/ss_pmlng_ingest.xlsx
@@ -2100,12 +2100,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[N-1] Kapasitor GI 150 kV Pemalang beroperasi menggunakan 1 PMS busbar</t>
+          <t>[BELUM_DITETAPKAN] Kapasitor GI 150 kV Pemalang beroperasi menggunakan 1 PMS busbar</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[N-1] Tegangan rendah pada wilayah Tegal yaitu pada GI 150 kV Kebasen dan GI 150 kV Brebes saat periode outage PLTU CEP. Serta adanya rencana pembangunan GI Brebes II yang berpotensimenambah pembebanan dan menurunkan kualitas tegangan di GI Brebes</t>
+          <t>[BELUM_DITETAPKAN] Tegangan rendah pada wilayah Tegal yaitu pada GI 150 kV Kebasen dan GI 150 kV Brebes saat periode outage PLTU CEP. Serta adanya rencana pembangunan GI Brebes II yang berpotensimenambah pembebanan dan menurunkan kualitas tegangan di GI Brebes</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
